--- a/Assets/@Resources/Data/Excel/PlayerStatusData.xlsx
+++ b/Assets/@Resources/Data/Excel/PlayerStatusData.xlsx
@@ -923,7 +923,7 @@
         <v>120</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>140</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>160</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>180</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>220</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>240</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>260</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>280</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>300</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>320</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1869,7 +1869,7 @@
         <v>340</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>360</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
         <v>380</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>400</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>420</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>440</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2385,7 +2385,7 @@
         <v>460</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>480</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>500</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2643,7 +2643,7 @@
         <v>520</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2729,7 +2729,7 @@
         <v>540</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2815,7 +2815,7 @@
         <v>560</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2901,7 +2901,7 @@
         <v>580</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2987,7 +2987,7 @@
         <v>600</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>620</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3159,7 +3159,7 @@
         <v>640</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>660</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>680</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3417,7 +3417,7 @@
         <v>700</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>720</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         <v>740</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>760</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -3761,7 +3761,7 @@
         <v>780</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>800</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>820</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>840</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         <v>860</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>880</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
         <v>915</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>950</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4449,7 +4449,7 @@
         <v>985</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4535,7 +4535,7 @@
         <v>1020</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
         <v>1055</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -4707,7 +4707,7 @@
         <v>1090</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>1125</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>1160</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -4965,7 +4965,7 @@
         <v>1195</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         <v>1230</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -5137,7 +5137,7 @@
         <v>1265</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -5223,7 +5223,7 @@
         <v>1300</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
         <v>1335</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         <v>1370</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
         <v>1405</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>1440</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>1475</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>1510</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -5825,7 +5825,7 @@
         <v>1545</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -5911,7 +5911,7 @@
         <v>1580</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>1615</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -6083,7 +6083,7 @@
         <v>1650</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>1685</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>1720</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -6341,7 +6341,7 @@
         <v>1755</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
         <v>1790</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -6513,7 +6513,7 @@
         <v>1825</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -6599,7 +6599,7 @@
         <v>1860</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
         <v>1895</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>1930</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
         <v>1965</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
         <v>2000</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>2035</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -7115,7 +7115,7 @@
         <v>2070</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -7201,7 +7201,7 @@
         <v>2105</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
         <v>2140</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -7373,7 +7373,7 @@
         <v>2175</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -7459,7 +7459,7 @@
         <v>2210</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -7545,7 +7545,7 @@
         <v>2245</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
         <v>2280</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -7717,7 +7717,7 @@
         <v>2315</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -7803,7 +7803,7 @@
         <v>2350</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -7889,7 +7889,7 @@
         <v>2385</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>2420</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
         <v>2455</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -8147,7 +8147,7 @@
         <v>2490</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -8233,7 +8233,7 @@
         <v>2525</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -8319,7 +8319,7 @@
         <v>2560</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -8405,7 +8405,7 @@
         <v>2595</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -8491,7 +8491,7 @@
         <v>2630</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -8577,7 +8577,7 @@
         <v>2665</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>2700</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -8749,7 +8749,7 @@
         <v>2735</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -8835,7 +8835,7 @@
         <v>2770</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
@@ -8921,7 +8921,7 @@
         <v>2805</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
         <v>2840</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -9093,7 +9093,7 @@
         <v>2875</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -9179,7 +9179,7 @@
         <v>2910</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -9265,7 +9265,7 @@
         <v>2945</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -9351,7 +9351,7 @@
         <v>2980</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>3040</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -9523,7 +9523,7 @@
         <v>3100</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -9609,7 +9609,7 @@
         <v>3160</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -9695,7 +9695,7 @@
         <v>3220</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -9781,7 +9781,7 @@
         <v>3280</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
         <v>3340</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
@@ -9953,7 +9953,7 @@
         <v>3400</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -10039,7 +10039,7 @@
         <v>3460</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -10125,7 +10125,7 @@
         <v>3520</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -10211,7 +10211,7 @@
         <v>3580</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -10297,7 +10297,7 @@
         <v>3640</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -10383,7 +10383,7 @@
         <v>3700</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -10469,7 +10469,7 @@
         <v>3760</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -10555,7 +10555,7 @@
         <v>3820</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -10641,7 +10641,7 @@
         <v>3880</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -10727,7 +10727,7 @@
         <v>3940</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -10813,7 +10813,7 @@
         <v>4000</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -10899,7 +10899,7 @@
         <v>4060</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -10985,7 +10985,7 @@
         <v>4120</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -11071,7 +11071,7 @@
         <v>4180</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>4240</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -11243,7 +11243,7 @@
         <v>4300</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -11329,7 +11329,7 @@
         <v>4360</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -11415,7 +11415,7 @@
         <v>4420</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -11501,7 +11501,7 @@
         <v>4480</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -11587,7 +11587,7 @@
         <v>4540</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -11673,7 +11673,7 @@
         <v>4600</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -11759,7 +11759,7 @@
         <v>4660</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -11845,7 +11845,7 @@
         <v>4720</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -11931,7 +11931,7 @@
         <v>4780</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
@@ -12017,7 +12017,7 @@
         <v>4840</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
@@ -12103,7 +12103,7 @@
         <v>4900</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
@@ -12189,7 +12189,7 @@
         <v>4960</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
@@ -12275,7 +12275,7 @@
         <v>5020</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
@@ -12361,7 +12361,7 @@
         <v>5080</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
@@ -12447,7 +12447,7 @@
         <v>5140</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -12533,7 +12533,7 @@
         <v>5200</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
@@ -12619,7 +12619,7 @@
         <v>5260</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -12705,7 +12705,7 @@
         <v>5320</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -12791,7 +12791,7 @@
         <v>5380</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -12877,7 +12877,7 @@
         <v>5440</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -12963,7 +12963,7 @@
         <v>5500</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
         <v>5560</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -13135,7 +13135,7 @@
         <v>5620</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -13221,7 +13221,7 @@
         <v>5680</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
@@ -13307,7 +13307,7 @@
         <v>5740</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
@@ -13393,7 +13393,7 @@
         <v>5800</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -13479,7 +13479,7 @@
         <v>5860</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
@@ -13565,7 +13565,7 @@
         <v>5920</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>5980</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -13737,7 +13737,7 @@
         <v>6040</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -13823,7 +13823,7 @@
         <v>6100</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
@@ -13909,7 +13909,7 @@
         <v>6160</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
@@ -13995,7 +13995,7 @@
         <v>6220</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -14081,7 +14081,7 @@
         <v>6280</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
@@ -14167,7 +14167,7 @@
         <v>6340</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
@@ -14253,7 +14253,7 @@
         <v>6400</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
@@ -14339,7 +14339,7 @@
         <v>6460</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
@@ -14425,7 +14425,7 @@
         <v>6520</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
@@ -14511,7 +14511,7 @@
         <v>6580</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -14597,7 +14597,7 @@
         <v>6640</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -14683,7 +14683,7 @@
         <v>6700</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I165" t="n">
         <v>0</v>
@@ -14769,7 +14769,7 @@
         <v>6760</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
@@ -14855,7 +14855,7 @@
         <v>6820</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -14941,7 +14941,7 @@
         <v>6880</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -15027,7 +15027,7 @@
         <v>6940</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -15113,7 +15113,7 @@
         <v>7000</v>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
@@ -15199,7 +15199,7 @@
         <v>7060</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
@@ -15285,7 +15285,7 @@
         <v>7120</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
@@ -15371,7 +15371,7 @@
         <v>7180</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
@@ -15457,7 +15457,7 @@
         <v>7240</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
@@ -15543,7 +15543,7 @@
         <v>7300</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
         <v>7360</v>
       </c>
       <c r="H176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
@@ -15715,7 +15715,7 @@
         <v>7420</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
@@ -15801,7 +15801,7 @@
         <v>7480</v>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
@@ -15887,7 +15887,7 @@
         <v>7540</v>
       </c>
       <c r="H179" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
@@ -15973,7 +15973,7 @@
         <v>7600</v>
       </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
@@ -16059,7 +16059,7 @@
         <v>7660</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>7720</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
@@ -16231,7 +16231,7 @@
         <v>7780</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
@@ -16317,7 +16317,7 @@
         <v>7880</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
@@ -16403,7 +16403,7 @@
         <v>7980</v>
       </c>
       <c r="H185" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
@@ -16489,7 +16489,7 @@
         <v>8080</v>
       </c>
       <c r="H186" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
@@ -16575,7 +16575,7 @@
         <v>8180</v>
       </c>
       <c r="H187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
@@ -16661,7 +16661,7 @@
         <v>8280</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
@@ -16747,7 +16747,7 @@
         <v>8380</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
@@ -16833,7 +16833,7 @@
         <v>8480</v>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -16919,7 +16919,7 @@
         <v>8580</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
@@ -17005,7 +17005,7 @@
         <v>8680</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
@@ -17091,7 +17091,7 @@
         <v>8780</v>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I193" t="n">
         <v>0</v>
@@ -17177,7 +17177,7 @@
         <v>8880</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
@@ -17263,7 +17263,7 @@
         <v>8980</v>
       </c>
       <c r="H195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
@@ -17349,7 +17349,7 @@
         <v>9080</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
@@ -17435,7 +17435,7 @@
         <v>9180</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
         <v>9280</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
@@ -17607,7 +17607,7 @@
         <v>9380</v>
       </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I199" t="n">
         <v>0</v>
@@ -17693,7 +17693,7 @@
         <v>9480</v>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
@@ -17779,7 +17779,7 @@
         <v>9580</v>
       </c>
       <c r="H201" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
@@ -17865,7 +17865,7 @@
         <v>9680</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -17951,7 +17951,7 @@
         <v>9780</v>
       </c>
       <c r="H203" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -18037,7 +18037,7 @@
         <v>9880</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
@@ -18123,7 +18123,7 @@
         <v>9980</v>
       </c>
       <c r="H205" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -18209,7 +18209,7 @@
         <v>10080</v>
       </c>
       <c r="H206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -18295,7 +18295,7 @@
         <v>10180</v>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
@@ -18381,7 +18381,7 @@
         <v>10280</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
@@ -18467,7 +18467,7 @@
         <v>10380</v>
       </c>
       <c r="H209" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -18553,7 +18553,7 @@
         <v>10480</v>
       </c>
       <c r="H210" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
@@ -18639,7 +18639,7 @@
         <v>10580</v>
       </c>
       <c r="H211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
@@ -18725,7 +18725,7 @@
         <v>10680</v>
       </c>
       <c r="H212" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I212" t="n">
         <v>0</v>
@@ -18811,7 +18811,7 @@
         <v>10780</v>
       </c>
       <c r="H213" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I213" t="n">
         <v>0</v>
@@ -18897,7 +18897,7 @@
         <v>10880</v>
       </c>
       <c r="H214" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I214" t="n">
         <v>0</v>
@@ -18983,7 +18983,7 @@
         <v>10980</v>
       </c>
       <c r="H215" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I215" t="n">
         <v>0</v>
@@ -19069,7 +19069,7 @@
         <v>11080</v>
       </c>
       <c r="H216" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I216" t="n">
         <v>0</v>
@@ -19155,7 +19155,7 @@
         <v>11180</v>
       </c>
       <c r="H217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I217" t="n">
         <v>0</v>
@@ -19241,7 +19241,7 @@
         <v>11280</v>
       </c>
       <c r="H218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I218" t="n">
         <v>0</v>
@@ -19327,7 +19327,7 @@
         <v>11380</v>
       </c>
       <c r="H219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I219" t="n">
         <v>0</v>
@@ -19413,7 +19413,7 @@
         <v>11480</v>
       </c>
       <c r="H220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I220" t="n">
         <v>0</v>
@@ -19499,7 +19499,7 @@
         <v>11580</v>
       </c>
       <c r="H221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I221" t="n">
         <v>0</v>
@@ -19585,7 +19585,7 @@
         <v>11680</v>
       </c>
       <c r="H222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I222" t="n">
         <v>0</v>
@@ -19671,7 +19671,7 @@
         <v>11780</v>
       </c>
       <c r="H223" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I223" t="n">
         <v>0</v>
@@ -19757,7 +19757,7 @@
         <v>11880</v>
       </c>
       <c r="H224" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I224" t="n">
         <v>0</v>
@@ -19843,7 +19843,7 @@
         <v>11980</v>
       </c>
       <c r="H225" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I225" t="n">
         <v>0</v>
@@ -19929,7 +19929,7 @@
         <v>12080</v>
       </c>
       <c r="H226" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -20015,7 +20015,7 @@
         <v>12180</v>
       </c>
       <c r="H227" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
@@ -20101,7 +20101,7 @@
         <v>12280</v>
       </c>
       <c r="H228" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -20187,7 +20187,7 @@
         <v>12380</v>
       </c>
       <c r="H229" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
@@ -20273,7 +20273,7 @@
         <v>12480</v>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -20359,7 +20359,7 @@
         <v>12580</v>
       </c>
       <c r="H231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -20445,7 +20445,7 @@
         <v>12680</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -20531,7 +20531,7 @@
         <v>12780</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -20617,7 +20617,7 @@
         <v>12880</v>
       </c>
       <c r="H234" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -20703,7 +20703,7 @@
         <v>12980</v>
       </c>
       <c r="H235" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -20789,7 +20789,7 @@
         <v>13080</v>
       </c>
       <c r="H236" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
         <v>13180</v>
       </c>
       <c r="H237" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
@@ -20961,7 +20961,7 @@
         <v>13280</v>
       </c>
       <c r="H238" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
@@ -21047,7 +21047,7 @@
         <v>13380</v>
       </c>
       <c r="H239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>13480</v>
       </c>
       <c r="H240" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
@@ -21219,7 +21219,7 @@
         <v>13580</v>
       </c>
       <c r="H241" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
@@ -21305,7 +21305,7 @@
         <v>13680</v>
       </c>
       <c r="H242" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I242" t="n">
         <v>0</v>
@@ -21391,7 +21391,7 @@
         <v>13780</v>
       </c>
       <c r="H243" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
@@ -21477,7 +21477,7 @@
         <v>13880</v>
       </c>
       <c r="H244" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I244" t="n">
         <v>0</v>
@@ -21563,7 +21563,7 @@
         <v>13980</v>
       </c>
       <c r="H245" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I245" t="n">
         <v>0</v>
@@ -21649,7 +21649,7 @@
         <v>14080</v>
       </c>
       <c r="H246" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I246" t="n">
         <v>0</v>
@@ -21735,7 +21735,7 @@
         <v>14180</v>
       </c>
       <c r="H247" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I247" t="n">
         <v>0</v>
@@ -21821,7 +21821,7 @@
         <v>14280</v>
       </c>
       <c r="H248" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I248" t="n">
         <v>0</v>
@@ -21907,7 +21907,7 @@
         <v>14380</v>
       </c>
       <c r="H249" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I249" t="n">
         <v>0</v>
@@ -21993,7 +21993,7 @@
         <v>14480</v>
       </c>
       <c r="H250" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I250" t="n">
         <v>0</v>
@@ -22079,7 +22079,7 @@
         <v>14580</v>
       </c>
       <c r="H251" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I251" t="n">
         <v>0</v>
@@ -22165,7 +22165,7 @@
         <v>14680</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I252" t="n">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>14780</v>
       </c>
       <c r="H253" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I253" t="n">
         <v>0</v>
@@ -22337,7 +22337,7 @@
         <v>14940</v>
       </c>
       <c r="H254" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I254" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
         <v>15100</v>
       </c>
       <c r="H255" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I255" t="n">
         <v>0</v>
@@ -22509,7 +22509,7 @@
         <v>15260</v>
       </c>
       <c r="H256" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I256" t="n">
         <v>0</v>
@@ -22595,7 +22595,7 @@
         <v>15420</v>
       </c>
       <c r="H257" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I257" t="n">
         <v>0</v>
@@ -22681,7 +22681,7 @@
         <v>15580</v>
       </c>
       <c r="H258" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I258" t="n">
         <v>0</v>
@@ -22767,7 +22767,7 @@
         <v>15740</v>
       </c>
       <c r="H259" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I259" t="n">
         <v>0</v>
@@ -22853,7 +22853,7 @@
         <v>15900</v>
       </c>
       <c r="H260" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I260" t="n">
         <v>0</v>
@@ -22939,7 +22939,7 @@
         <v>16060</v>
       </c>
       <c r="H261" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
@@ -23025,7 +23025,7 @@
         <v>16220</v>
       </c>
       <c r="H262" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I262" t="n">
         <v>0</v>
@@ -23111,7 +23111,7 @@
         <v>16380</v>
       </c>
       <c r="H263" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I263" t="n">
         <v>0</v>
@@ -23197,7 +23197,7 @@
         <v>16540</v>
       </c>
       <c r="H264" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I264" t="n">
         <v>0</v>
@@ -23283,7 +23283,7 @@
         <v>16700</v>
       </c>
       <c r="H265" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I265" t="n">
         <v>0</v>
@@ -23369,7 +23369,7 @@
         <v>16860</v>
       </c>
       <c r="H266" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I266" t="n">
         <v>0</v>
@@ -23455,7 +23455,7 @@
         <v>17020</v>
       </c>
       <c r="H267" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I267" t="n">
         <v>0</v>
@@ -23541,7 +23541,7 @@
         <v>17180</v>
       </c>
       <c r="H268" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I268" t="n">
         <v>0</v>
@@ -23627,7 +23627,7 @@
         <v>17340</v>
       </c>
       <c r="H269" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I269" t="n">
         <v>0</v>
@@ -23713,7 +23713,7 @@
         <v>17500</v>
       </c>
       <c r="H270" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I270" t="n">
         <v>0</v>
@@ -23799,7 +23799,7 @@
         <v>17660</v>
       </c>
       <c r="H271" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I271" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>17820</v>
       </c>
       <c r="H272" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I272" t="n">
         <v>0</v>
@@ -23971,7 +23971,7 @@
         <v>17980</v>
       </c>
       <c r="H273" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I273" t="n">
         <v>0</v>
@@ -24057,7 +24057,7 @@
         <v>18140</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I274" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>18300</v>
       </c>
       <c r="H275" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I275" t="n">
         <v>0</v>
@@ -24229,7 +24229,7 @@
         <v>18460</v>
       </c>
       <c r="H276" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I276" t="n">
         <v>0</v>
@@ -24315,7 +24315,7 @@
         <v>18620</v>
       </c>
       <c r="H277" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I277" t="n">
         <v>0</v>
@@ -24401,7 +24401,7 @@
         <v>18780</v>
       </c>
       <c r="H278" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I278" t="n">
         <v>0</v>
@@ -24487,7 +24487,7 @@
         <v>18940</v>
       </c>
       <c r="H279" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I279" t="n">
         <v>0</v>
@@ -24573,7 +24573,7 @@
         <v>19100</v>
       </c>
       <c r="H280" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I280" t="n">
         <v>0</v>
@@ -24659,7 +24659,7 @@
         <v>19260</v>
       </c>
       <c r="H281" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I281" t="n">
         <v>0</v>
@@ -24745,7 +24745,7 @@
         <v>19420</v>
       </c>
       <c r="H282" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I282" t="n">
         <v>0</v>
@@ -24831,7 +24831,7 @@
         <v>19580</v>
       </c>
       <c r="H283" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I283" t="n">
         <v>0</v>
@@ -24917,7 +24917,7 @@
         <v>19740</v>
       </c>
       <c r="H284" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I284" t="n">
         <v>0</v>
@@ -25003,7 +25003,7 @@
         <v>19900</v>
       </c>
       <c r="H285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I285" t="n">
         <v>0</v>
@@ -25089,7 +25089,7 @@
         <v>20060</v>
       </c>
       <c r="H286" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I286" t="n">
         <v>0</v>
@@ -25175,7 +25175,7 @@
         <v>20220</v>
       </c>
       <c r="H287" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I287" t="n">
         <v>0</v>
@@ -25261,7 +25261,7 @@
         <v>20380</v>
       </c>
       <c r="H288" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I288" t="n">
         <v>0</v>
@@ -25347,7 +25347,7 @@
         <v>20540</v>
       </c>
       <c r="H289" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I289" t="n">
         <v>0</v>
@@ -25433,7 +25433,7 @@
         <v>20700</v>
       </c>
       <c r="H290" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I290" t="n">
         <v>0</v>
@@ -25519,7 +25519,7 @@
         <v>20860</v>
       </c>
       <c r="H291" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I291" t="n">
         <v>0</v>
@@ -25605,7 +25605,7 @@
         <v>21020</v>
       </c>
       <c r="H292" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I292" t="n">
         <v>0</v>
@@ -25691,7 +25691,7 @@
         <v>21180</v>
       </c>
       <c r="H293" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I293" t="n">
         <v>0</v>
@@ -25777,7 +25777,7 @@
         <v>21340</v>
       </c>
       <c r="H294" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I294" t="n">
         <v>0</v>
@@ -25863,7 +25863,7 @@
         <v>21500</v>
       </c>
       <c r="H295" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I295" t="n">
         <v>0</v>
@@ -25949,7 +25949,7 @@
         <v>21660</v>
       </c>
       <c r="H296" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I296" t="n">
         <v>0</v>
@@ -26035,7 +26035,7 @@
         <v>21820</v>
       </c>
       <c r="H297" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I297" t="n">
         <v>0</v>
@@ -26121,7 +26121,7 @@
         <v>21980</v>
       </c>
       <c r="H298" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I298" t="n">
         <v>0</v>
@@ -26207,7 +26207,7 @@
         <v>22140</v>
       </c>
       <c r="H299" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I299" t="n">
         <v>0</v>
@@ -26293,7 +26293,7 @@
         <v>22300</v>
       </c>
       <c r="H300" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I300" t="n">
         <v>0</v>
@@ -26379,7 +26379,7 @@
         <v>22460</v>
       </c>
       <c r="H301" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I301" t="n">
         <v>0</v>
@@ -26465,7 +26465,7 @@
         <v>22620</v>
       </c>
       <c r="H302" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I302" t="n">
         <v>0</v>
@@ -26551,7 +26551,7 @@
         <v>22780</v>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
